--- a/artfynd/A 27577-2022 artfynd.xlsx
+++ b/artfynd/A 27577-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27577-2022 artfynd.xlsx
+++ b/artfynd/A 27577-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101518122</v>
+        <v>101518251</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488574.2918541323</v>
+        <v>488524</v>
       </c>
       <c r="R2" t="n">
-        <v>7037824.95849665</v>
+        <v>7038079</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101518168</v>
+        <v>101518211</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488543.2764927606</v>
+        <v>488480</v>
       </c>
       <c r="R3" t="n">
-        <v>7037915.385141752</v>
+        <v>7037977</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101518285</v>
+        <v>101518264</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488287.0494584803</v>
+        <v>488505</v>
       </c>
       <c r="R4" t="n">
-        <v>7039218.005914037</v>
+        <v>7038255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,19 +951,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,42 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101518238</v>
+        <v>101518168</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488471.2908947759</v>
+        <v>488543</v>
       </c>
       <c r="R5" t="n">
-        <v>7038065.419353546</v>
+        <v>7037916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,19 +1053,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101518264</v>
+        <v>101518285</v>
       </c>
       <c r="B6" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488505.1015926914</v>
+        <v>488287</v>
       </c>
       <c r="R6" t="n">
-        <v>7038254.853292226</v>
+        <v>7039218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,19 +1155,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,6 +1182,108 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101518122</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxforsvägen , Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488574</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037825</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27577-2022 artfynd.xlsx
+++ b/artfynd/A 27577-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518251</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518264</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518122</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>